--- a/results/Int Task Remove ACC 1.0/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 1.0/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.003699078708420611</v>
+        <v>0.000435082793325533</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.002806077404746727</v>
+        <v>-0.002709662198350161</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.001528397435354466</v>
+        <v>-0.0004575473092516312</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0002866568447232587</v>
+        <v>-0.0007782943040450829</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.002733518134013936</v>
+        <v>0.002164270543448957</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.004466684674183596</v>
+        <v>-0.00131325339950106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001029133503205981</v>
+        <v>6.042323233434899e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0002265698982057219</v>
+        <v>0.002778210614096599</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005207665387607595</v>
+        <v>0.004734673912261697</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004883238843195442</v>
+        <v>0.007890922465678921</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0001274024204261127</v>
+        <v>0.0006160483111699755</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0008760509996121213</v>
+        <v>-0.001099113535330871</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.002309625260967518</v>
+        <v>0.0005495974790591096</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003627599741460257</v>
+        <v>0.003428284886036345</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007542731578268421</v>
+        <v>0.006738154939903787</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007223677859052368</v>
+        <v>0.001841362473677906</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001259368663195825</v>
+        <v>0.0009123761208089554</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001158517323572386</v>
+        <v>0.0006167237583130403</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.001119206891574651</v>
+        <v>-0.0008954893473771574</v>
       </c>
       <c r="V3" t="n">
-        <v>7.604991906434822e-05</v>
+        <v>0.0001428482350401306</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00179375313850217</v>
+        <v>0.0007827285727488442</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.001626551238177534</v>
+        <v>0.001693672006856692</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001432081956120423</v>
+        <v>-5.905412557422158e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.000703882256414361</v>
+        <v>0.0001954485073034329</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0005608540979766329</v>
+        <v>0.00105357511248303</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.701690606377705e-05</v>
+        <v>0.0002572620109567225</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0009156050838033246</v>
+        <v>0.000969753595297428</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.002735486511083558</v>
+        <v>-0.001334903316683757</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.000892280754221122</v>
+        <v>0.0004487524165509527</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.001704777480453018</v>
+        <v>-0.000489340661103185</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0005233502472124552</v>
+        <v>0.0001833155951221288</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0001674956193210331</v>
+        <v>5.550181756955871e-06</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.001619555357488784</v>
+        <v>0.0004037425657696835</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.0008453818683044435</v>
+        <v>0.0007037373093021958</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4.082578382813672e-05</v>
+        <v>8.345634278179802e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0002300873325444553</v>
+        <v>-0.0003600911084764169</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001062021875315455</v>
+        <v>0.0006150930564169088</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.256483070859019e-05</v>
+        <v>0.001172520796100452</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0004749004774045218</v>
+        <v>-0.0001303163711779098</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001478179571183927</v>
+        <v>0.0003667469043244742</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0007143696835944979</v>
+        <v>0.0004865685437608892</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.0001802381222277548</v>
+        <v>0.000457090331006308</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.003207409392523373</v>
+        <v>-0.002851991106467584</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.004935500978958869</v>
+        <v>-0.0005222246199645109</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.001380146996498833</v>
+        <v>-0.0007156097228773905</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.001896529621727012</v>
+        <v>-0.0004676798834870223</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0003138361881057861</v>
+        <v>-0.00015872210940711</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.001680750917932042</v>
+        <v>0.0002841708155068623</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.005959935993517242</v>
+        <v>-0.001698155535367148</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.002203674906596376</v>
+        <v>-4.816179854761338e-05</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.004356054228058329</v>
+        <v>-0.0009337192441953265</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0001368782396605417</v>
+        <v>-8.298720688162397e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.00126335086291657</v>
+        <v>5.817694427086239e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.001185603846844186</v>
+        <v>-7.389079889071328e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.004625124030826844</v>
+        <v>-0.0003132281942325766</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.003807685846292344</v>
+        <v>-0.004248239850611445</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.983217104968072e-05</v>
+        <v>-0.0004579806674508291</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.001760103060080689</v>
+        <v>2.229565077406459e-05</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.002174691738366195</v>
+        <v>-0.001272135323949587</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0002449061369733385</v>
+        <v>-7.407902615143125e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0008693921858357755</v>
+        <v>9.643654692807815e-05</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.002954051793706885</v>
+        <v>-0.001697158146608638</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.005429532828620821</v>
+        <v>-0.002665023217497666</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.001144427204995643</v>
+        <v>-5.469112400497852e-05</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.877181190545476e-05</v>
+        <v>4.02293871129511e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.001290341619186733</v>
+        <v>-0.000153902528983243</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0007480598959214534</v>
+        <v>-0.0004640806208149551</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0004617749954564298</v>
+        <v>-8.963848741957771e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.001141168758684016</v>
+        <v>0.0001064943546476227</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001450272348353203</v>
+        <v>-2.558496272357382e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.00218873110350808</v>
+        <v>-0.0007536046139461272</v>
       </c>
       <c r="BX3" t="n">
-        <v>-2.410085100691406e-05</v>
+        <v>-2.963566734516809e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.0002298474631812786</v>
+        <v>-8.607944739605354e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.000240519976656508</v>
+        <v>0.0001893267995866787</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>1.642594564128408e-05</v>
+        <v>-0.0001422346385116679</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.002282219097233454</v>
+        <v>-0.0003891983799589039</v>
       </c>
       <c r="CD3" t="n">
-        <v>-5.347593582888388e-06</v>
+        <v>5.347593582887278e-06</v>
       </c>
       <c r="CE3" t="n">
-        <v>3.66531199261222e-05</v>
+        <v>0.0002297932810024927</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0002563578753547469</v>
+        <v>-0.0003451256602398833</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.001890142095655454</v>
+        <v>-0.0006083351921733406</v>
       </c>
       <c r="CH3" t="n">
-        <v>2.607677922157659e-05</v>
+        <v>8.603360138325412e-05</v>
       </c>
       <c r="CI3" t="n">
-        <v>-1.663334925126156e-05</v>
+        <v>0.000540878033548633</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.001587602796570559</v>
+        <v>-0.0003450123959828377</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.002042181399307741</v>
+        <v>-0.001064796345765338</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004208110876604296</v>
+        <v>0.002881089507180235</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004983372491430444</v>
+        <v>0.006197203970421407</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004834938320357335</v>
+        <v>0.003609520254513789</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00185407092063214</v>
+        <v>0.00103906296036536</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006006986820500011</v>
+        <v>0.00271153645412047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01181316883584532</v>
+        <v>0.006143933153086887</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002364649580840308</v>
+        <v>0.0001574968826463809</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004849219661963588</v>
+        <v>0.007018408256359639</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01208635768207754</v>
+        <v>0.01077605643049839</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01280258182054371</v>
+        <v>0.01013330438460911</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003299810343055662</v>
+        <v>0.0021664980052907</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004451673409725267</v>
+        <v>0.004555624661882984</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004246163261330258</v>
+        <v>0.001856373219255077</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01159291278990741</v>
+        <v>0.01101574204315608</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01445537387540791</v>
+        <v>0.01157747370020807</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004377326225933909</v>
+        <v>0.006005889350573585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004121138903490149</v>
+        <v>0.001916852388318316</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004445766940956707</v>
+        <v>0.002687846221948598</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005170050965183423</v>
+        <v>0.004229606905908644</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002748739684389323</v>
+        <v>0.0003786029036087757</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005471065946953329</v>
+        <v>0.002863457020044687</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002560627992498681</v>
+        <v>0.002552195167985188</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003162122664366916</v>
+        <v>0.001902647982834677</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002220987244641383</v>
+        <v>0.001726742221468</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002640014019271896</v>
+        <v>0.002665979837451433</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003313312359393668</v>
+        <v>0.0002427063412117121</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.006387225481664488</v>
+        <v>0.005857162462853311</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.00814528725971695</v>
+        <v>0.005510994239219449</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004226296320803914</v>
+        <v>0.001523458762568542</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.00331600392994625</v>
+        <v>0.001963153039478298</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001632841850196826</v>
+        <v>0.0003150147688097265</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0004393442264346393</v>
+        <v>0.0005013854957509227</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004757948635409186</v>
+        <v>0.00211503019306975</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.008334422901301914</v>
+        <v>0.007514318666559336</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0001633350823771489</v>
+        <v>0.0003159939882196536</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0006516707690850829</v>
+        <v>0.001677993181355748</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.004010734849051345</v>
+        <v>0.001847473382228687</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.006335570446321552</v>
+        <v>0.003370152293382357</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001241077079796308</v>
+        <v>0.0007476881937969372</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003599786396108494</v>
+        <v>0.001874531397893509</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.002192017277038588</v>
+        <v>0.002968297166291552</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002016982876996494</v>
+        <v>0.001430330622973928</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.005766519160050635</v>
+        <v>0.003533144973539286</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.01114262830853724</v>
+        <v>0.005950069859174506</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002404649014416442</v>
+        <v>0.001655041719612998</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.003247123039834078</v>
+        <v>0.002726104482544448</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.00115687502998174</v>
+        <v>0.0007023237021037251</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002981203563493844</v>
+        <v>0.002328987335151807</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.007124698885184025</v>
+        <v>0.002869229976176384</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.00723522782959289</v>
+        <v>0.005934858809522751</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0081326292273887</v>
+        <v>0.006016196260219644</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0005828961081215653</v>
+        <v>0.000321705487381812</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.002356525387078819</v>
+        <v>0.0004196253769187858</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0042762831543768</v>
+        <v>0.004345525376982416</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.01065930294007447</v>
+        <v>0.003965500530636885</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004083916833771092</v>
+        <v>0.004028518404421599</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0007587014741963921</v>
+        <v>0.0005514066823311802</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002312905367249419</v>
+        <v>0.001851548089216457</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.008891066696909672</v>
+        <v>0.00389756876227114</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0005668131117106991</v>
+        <v>0.0009440765400661592</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.003002696150891139</v>
+        <v>0.001993434538961827</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.009193492933381829</v>
+        <v>0.00457792415402257</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.01431717062047643</v>
+        <v>0.01235317991535626</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.003508613067275288</v>
+        <v>0.001336169258446551</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0001611784127550975</v>
+        <v>0.0001547151108215569</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.002391519713024778</v>
+        <v>0.001504186611917675</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.002789435432413577</v>
+        <v>0.00216284666974193</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001496470900583755</v>
+        <v>0.001108748079425166</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.002741108452899604</v>
+        <v>0.001429010133442935</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003645008536708441</v>
+        <v>0.001871862104732422</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.005555483949742039</v>
+        <v>0.002645666887857957</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.000144390834862684</v>
+        <v>0.0001318950967182781</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0006895911704647164</v>
+        <v>0.0003093519476708173</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001136631961800633</v>
+        <v>0.0003696165703187353</v>
       </c>
       <c r="CA4" t="n">
         <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0006407993608224117</v>
+        <v>0.0004707114442330905</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.006208544589630543</v>
+        <v>0.001117539059505761</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.691057572282773e-05</v>
+        <v>1.691057572282422e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0002247808136226182</v>
+        <v>0.0007059519500351999</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0007062817148205304</v>
+        <v>0.002135440654293185</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.005627736509550404</v>
+        <v>0.001290675610511638</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0003912401864999557</v>
+        <v>0.0003023238696144862</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001180425489496788</v>
+        <v>0.001151250838346023</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.004711201304905011</v>
+        <v>0.002373720480298994</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.003949601758015128</v>
+        <v>0.00289650028737882</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01080645161290316</v>
+        <v>-0.003767660910517989</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01128563118091914</v>
+        <v>-0.01745454545454546</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01297265852239673</v>
+        <v>-0.009656777196044197</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.004223968565815306</v>
+        <v>-0.002689618074233502</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.01854545454545455</v>
+        <v>-0.0004812834224599327</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03751515151515154</v>
+        <v>-0.01806060606060608</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0002326934264107017</v>
+        <v>-0.0001691093573844227</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.006806282722513113</v>
+        <v>-0.002714681440443245</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02138504155124655</v>
+        <v>-0.01961668545659522</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.02299168975069254</v>
+        <v>-0.01048478015783537</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.004421175101803365</v>
+        <v>-0.001551246537396145</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01000581733566028</v>
+        <v>-0.01109090909090916</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0112465373961219</v>
+        <v>-0.001412429378531033</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01552062868369349</v>
+        <v>-0.01394891944990175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.008104125736738677</v>
+        <v>-0.005298759864712499</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.003955788248981939</v>
+        <v>-0.005817335660267542</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01076207097149506</v>
+        <v>-0.001726844583987375</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.005337519623233866</v>
+        <v>-0.00203606748109364</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.01218836565096955</v>
+        <v>-0.01180919139034322</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0001108033240997175</v>
+        <v>-5.636978579480756e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.004911591355599187</v>
+        <v>-0.002268760907504342</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.005991855730075634</v>
+        <v>-0.002818489289740678</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.004125736738703323</v>
+        <v>-0.003043968432919919</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.001424361493123716</v>
+        <v>-0.001506186121570763</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.003094302554027517</v>
+        <v>-0.002259332023575633</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0004812834224599327</v>
+        <v>-5.376344086022167e-05</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.01542239685658151</v>
+        <v>-0.01247544204322198</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.02145454545454548</v>
+        <v>-0.01617812852311161</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.008424242424242478</v>
+        <v>-0.00214205186020292</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.00822580645161286</v>
+        <v>-0.004002254791431759</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.005151515151515185</v>
+        <v>-5.817335660267542e-05</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0005882352941176782</v>
+        <v>-0.0008455467869221689</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01387878787878792</v>
+        <v>-0.004171364148816204</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01561443066516341</v>
+        <v>-0.01583990980834272</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0002770083102492937</v>
+        <v>-0.0002946954813359048</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.001878787878787891</v>
+        <v>-0.004666666666666697</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.004303030303030331</v>
+        <v>-0.001098901098901028</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01357575757575761</v>
+        <v>-0.005355129650507296</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.003548574752763212</v>
+        <v>-0.001030303030303037</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.002946954813359526</v>
+        <v>-0.001521984216459959</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.002471751412429324</v>
+        <v>-0.00545454545454549</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.004960707269155184</v>
+        <v>-0.002326934264107017</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01349462365591392</v>
+        <v>-0.009864712514092423</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.03084479371316306</v>
+        <v>-0.01409626719056972</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.006907378335949709</v>
+        <v>-0.003929273084479346</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.008267922553636797</v>
+        <v>-0.004195804195804254</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.003575757575757599</v>
+        <v>-0.001575757575757586</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.008787878787878844</v>
+        <v>-0.004604918890633136</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.02000000000000003</v>
+        <v>-0.006031567080045086</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01556974459724947</v>
+        <v>-0.006595264937993217</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.0159135559921414</v>
+        <v>-0.008399098083427269</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0005913978494623163</v>
+        <v>-0.000698080279232105</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.007575757575757625</v>
+        <v>-0.0007878787878787929</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.01011787819253434</v>
+        <v>-0.01051080550098233</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.02252688172043005</v>
+        <v>-0.006139489194499015</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.012475442043222</v>
+        <v>-0.01430876815492205</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001375245579567741</v>
+        <v>-0.001451612903225874</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.007311827956989192</v>
+        <v>-0.002242424242424257</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01806451612903219</v>
+        <v>-0.009244644870349461</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001176470588235368</v>
+        <v>-0.002484848484848501</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.005808477237048626</v>
+        <v>-0.001505376344086062</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.02868369351669939</v>
+        <v>-0.008606060606060662</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.04327111984282904</v>
+        <v>-0.03344793713163065</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.008254847645429353</v>
+        <v>-0.002606060606060623</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0001046572475143837</v>
+        <v>-0.000181818181818183</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.005706371191135739</v>
+        <v>-0.002797202797202825</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.005983379501385055</v>
+        <v>-0.004626143087681578</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.00198848770277339</v>
+        <v>-0.002197802197802134</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.006149584487534654</v>
+        <v>-0.002152414194298991</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.007922437673130223</v>
+        <v>-0.002582033351264168</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.01246537396121886</v>
+        <v>-0.007638515330823071</v>
       </c>
       <c r="BX5" t="n">
+        <v>-0.0003945885005636751</v>
+      </c>
+      <c r="BY5" t="n">
         <v>-0.0004072134962187279</v>
       </c>
-      <c r="BY5" t="n">
-        <v>-0.001726844583987408</v>
-      </c>
       <c r="BZ5" t="n">
-        <v>-0.001021505376344045</v>
+        <v>-0.0005649717514123909</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.0006993006993007422</v>
+        <v>-0.001183431952662739</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.01939393939393942</v>
+        <v>-0.002909090909090928</v>
       </c>
       <c r="CD5" t="n">
-        <v>-5.347593582888388e-05</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0003763440860214739</v>
+        <v>-0.0007326007326006855</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.001075847229693427</v>
+        <v>-0.0060606060606061</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.01357575757575762</v>
+        <v>-0.003878787878787904</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0006355932203389147</v>
+        <v>-0.000343811394891913</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.00132963988919671</v>
+        <v>-0.001409244644870333</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.0129639889196676</v>
+        <v>-0.005515151515151551</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.0111515151515152</v>
+        <v>-0.009090909090909127</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.005998138873698241</v>
+        <v>-0.0007221204539362258</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.005659420749096866</v>
+        <v>-0.005284379253512583</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002443081322891566</v>
+        <v>-0.001023967884811958</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001076749467394839</v>
+        <v>-0.001210965588084201</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.003706791262167805</v>
+        <v>-0.000348907477117652</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.002715426086438513</v>
+        <v>-0.001079467619959135</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.002370899776914789</v>
+        <v>-0.0006551593203177247</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002221246378742014</v>
+        <v>0.002697173630623284</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.001038591215600462</v>
+        <v>0.002541542040545017</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.001589711464819657</v>
+        <v>-0.0008347487813148645</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003383723169449127</v>
+        <v>-0.001390383535067116</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.004037125178486428</v>
+        <v>-0.0008550784052474946</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.003260018448293551</v>
+        <v>-0.004143281746438482</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.004180183292722798</v>
+        <v>-0.001859354481462797</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.00199204587242397</v>
+        <v>-5.296610169488458e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.001973414434116954</v>
+        <v>-0.000407234022029418</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.001591532221517264</v>
+        <v>-0.001078186519362953</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0005701824406424527</v>
+        <v>-0.001173921417565479</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.296610169490957e-05</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0003707627118643836</v>
+        <v>-0.0009477568328460418</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002680261962018957</v>
+        <v>0.0002835520446969525</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0003344965573028713</v>
+        <v>-0.001413389700915801</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0009106347811131954</v>
+        <v>-0.000773760707125959</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.001536016949152527</v>
+        <v>-0.0006867125368599958</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0001209677419354738</v>
+        <v>6.700313261398527e-05</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.002682749278371346</v>
+        <v>-0.001173264356111611</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.00142110545096012</v>
+        <v>-0.0008848218694514936</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.002565672097281568</v>
+        <v>-0.0004407452130412715</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.004079576932762558</v>
+        <v>-0.001456317097678367</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0001735693009696199</v>
+        <v>-3.683693516698116e-05</v>
       </c>
       <c r="AH6" t="n">
-        <v>-6.604825763420197e-05</v>
+        <v>-0.0002006843816866194</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.00217146908391144</v>
+        <v>-0.0007055759366683401</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.0009656688088974491</v>
+        <v>-0.001218730173116994</v>
       </c>
       <c r="AL6" t="n">
-        <v>-9.953901329300686e-05</v>
+        <v>-9.09090909090915e-05</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0003919899041077507</v>
+        <v>-0.0006539546232334271</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0006198046216579128</v>
+        <v>-0.0006156920246104813</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.001614355285497265</v>
+        <v>-0.0006168716841165905</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0004881841731575465</v>
+        <v>-0.0005351234786718894</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0002667883587803871</v>
+        <v>-0.0008745472799264715</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.00078947368421054</v>
+        <v>-0.0009281245598384586</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0006018476661707461</v>
+        <v>-0.0003267759049720404</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.004531047084679119</v>
+        <v>-0.003959483297040914</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.004944018215834428</v>
+        <v>-0.001320549406203114</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.002457339277717835</v>
+        <v>-0.00137511530183457</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.003488017131401447</v>
+        <v>-0.002405871777991578</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>-0.0004021461117339503</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.002138877063211148</v>
+        <v>-0.0007019599821365408</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.006462798196212116</v>
+        <v>-0.003151611596270032</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.006152863379558315</v>
+        <v>-0.00382239189633313</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.01118555088910729</v>
+        <v>-0.004216899034080568</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0.0001256623206524754</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0009288760720851941</v>
+        <v>-0.0001007008951190686</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0002834867304083416</v>
+        <v>-0.0001350601883842007</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.01192461439006642</v>
+        <v>-0.003642440671190814</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.005624439662901225</v>
+        <v>-0.004894610929236995</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0002794354719436759</v>
+        <v>-0.0008205483121986046</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.002132153560724995</v>
+        <v>-0.001165842786826365</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.00464152876108268</v>
+        <v>-0.003629422686494696</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0005377522541383766</v>
+        <v>-0.0001962323390894694</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.002646281126401728</v>
+        <v>-0.0007750329339957007</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.00190956919818249</v>
+        <v>-0.004088240762323367</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.00351615475026093</v>
+        <v>-0.00284662256195512</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001177287192840012</v>
+        <v>-0.0006918439664882703</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001756961525869108</v>
+        <v>-0.0009899232358326654</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001657570917265636</v>
+        <v>-0.001462751534180101</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0001883704853204909</v>
+        <v>-0.0005169100260592807</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.002701782220106841</v>
+        <v>-0.0009687981510015208</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.003114161303966917</v>
+        <v>-0.001587215646772453</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.002197482991292715</v>
+        <v>-0.001302871648421378</v>
       </c>
       <c r="BX6" t="n">
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>-0.0003026831079826319</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0004182922171783788</v>
+        <v>-3.683693516697839e-05</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0002623605273374602</v>
+        <v>-0.0001751407380931214</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001493223069944785</v>
+        <v>-0.0008361279796972376</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>0</v>
+        <v>-8.455467869219468e-05</v>
       </c>
       <c r="CF6" t="n">
-        <v>-1.106157492046789e-05</v>
+        <v>-4.363001745201489e-05</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0005421056949506926</v>
+        <v>-0.0009473323051937072</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0001962323390894694</v>
+        <v>0</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0008486593013281113</v>
+        <v>-5.175496772132915e-05</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.003269316198635549</v>
+        <v>-0.0006052517348027531</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001347718209009357</v>
+        <v>-0.0006046572475143814</v>
       </c>
     </row>
     <row r="7">
@@ -2232,235 +2232,235 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.002666666666666706</v>
+        <v>0.0008444158243973376</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.000654778089972502</v>
+        <v>-0.0007349286588840154</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0001080593614530667</v>
+        <v>0.000135212772575416</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0002100522908735692</v>
+        <v>-0.0009115347018573249</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0009554291670443194</v>
+        <v>0.001360097392486032</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0007821577131503997</v>
+        <v>-0.0003692974576322339</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.688172043011083e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.001072694146357767</v>
+        <v>0.001092582467650816</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007335755642207314</v>
+        <v>0.004615945243678287</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008890479392328449</v>
+        <v>0.0104605175634952</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0004914118973406711</v>
+        <v>0.000170729980311346</v>
       </c>
       <c r="N7" t="n">
-        <v>4.055039183529791e-05</v>
+        <v>0.0009185260657506799</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.001958670484943309</v>
+        <v>5.232862375721959e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003229231823191276</v>
+        <v>0.0002825632897329067</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003688404483519131</v>
+        <v>0.001024615547297508</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0007400582610666672</v>
+        <v>0.0004961576266642509</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001662155074185046</v>
+        <v>0.0006256515652458493</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0004301075268817012</v>
+        <v>-3.189356661204002e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0003859069506658818</v>
+        <v>0.0001165370982634418</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.45579567780041e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001023561015149232</v>
+        <v>0.0001845850002532123</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.001122301334185422</v>
+        <v>0.001394804290731871</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001594921166623681</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.0003465927313853146</v>
+        <v>-8.310249307477702e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001454333915066885</v>
+        <v>0.0004748024043070232</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>0.0001864134419236274</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0004143008438385943</v>
+        <v>0.0005559423467195678</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.0001875970329480781</v>
+        <v>-0.0002922281171259921</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0009680795395080656</v>
+        <v>0.0005601443800889672</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0007338756884761378</v>
+        <v>-0.0004100601421541838</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.03030303030305e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.817335660267542e-05</v>
+        <v>2.455795677799855e-05</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.0004216894770234736</v>
+        <v>0.0008185684197634602</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0001881150523684094</v>
+        <v>0.001118264589195028</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-3.531073446328969e-05</v>
+        <v>5.540166204985875e-05</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0001985153746135226</v>
+        <v>-2.420309362383144e-06</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0002214379811416034</v>
+        <v>0.001154045195790898</v>
       </c>
       <c r="AP7" t="n">
-        <v>-5.376344086019946e-05</v>
+        <v>-0.000169991348284676</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0008516061511453677</v>
+        <v>-5.54016620498532e-05</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0004753212233276849</v>
+        <v>0.0005652925933184505</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0001328273244781741</v>
+        <v>0.00053590937841409</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.002938794978575915</v>
+        <v>-0.00188547584393633</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.002753405795173319</v>
+        <v>-0.0002063121043211491</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0004782244176561312</v>
+        <v>-0.0007853036666368885</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0002919376359223902</v>
+        <v>-0.0003626997794495268</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>-5.376344086022167e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0002419354838709475</v>
+        <v>1.604278074865962e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.005556210157406566</v>
+        <v>-0.002052169898430301</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.001506494236540729</v>
+        <v>-0.001166177908113419</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.00274520060637326</v>
+        <v>-0.002120523592438433</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.455795677799855e-05</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.000410757523348293</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>-5.347593582888388e-05</v>
+        <v>-2.770083102492937e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.001204632176768111</v>
+        <v>-0.0003671938729266576</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.002988966399649345</v>
+        <v>-0.003257023040119472</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>5.347593582887278e-05</v>
+        <v>-0.0004643611029809258</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.0008441123996431599</v>
+        <v>-0.0002493074792243588</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.001752469863137862</v>
+        <v>-0.0006064004954832502</v>
       </c>
       <c r="BL7" t="n">
-        <v>-5.376344086019391e-05</v>
+        <v>8.021390374330916e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0004635487773744672</v>
+        <v>-0.0005085992246514681</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.0006028653977898646</v>
+        <v>-0.001469546006100958</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.002280200089703632</v>
+        <v>0.0006561541766038903</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0003858681673451381</v>
+        <v>0.0001141864965726047</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.0006458654340010028</v>
+        <v>0.000259451736008548</v>
       </c>
       <c r="BS7" t="n">
-        <v>-5.376344086018281e-05</v>
+        <v>-0.0002759524456932228</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0002150537634408756</v>
+        <v>-4.533442682705391e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.0002121827752079863</v>
+        <v>2.372736072014383e-05</v>
       </c>
       <c r="BV7" t="n">
-        <v>-3.600392770116703e-05</v>
+        <v>-4.410106771006168e-05</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0.0005296610169491068</v>
+        <v>0.0002956989247311692</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>-0.000179159569684767</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-8.021390374332582e-05</v>
+        <v>0.0002741197209178148</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
@@ -2469,31 +2469,31 @@
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.0009006473402758619</v>
+        <v>-0.0002406323114036823</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>5.938970860436821e-05</v>
+        <v>5.379236148466138e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0003255530357470393</v>
+        <v>0.0002483446161138603</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0001069518716577844</v>
+        <v>-2.237794564155516e-05</v>
       </c>
       <c r="CH7" t="n">
-        <v>3.03030303030305e-05</v>
+        <v>5.58246462157741e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.0001604278074866516</v>
+        <v>0.0006148958480053868</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.0001052309035502241</v>
+        <v>0.0001335425615752783</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.00042739608932576</v>
+        <v>-0.0002712311315863636</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0007437106656454695</v>
+        <v>0.001288204861177494</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.541077969648701e-05</v>
+        <v>-0.000172777123175899</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003066301377716074</v>
+        <v>0.001732986646122245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0003899648008562711</v>
+        <v>-0.0004178352768263172</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003792501600282022</v>
+        <v>0.004914965986394576</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0003189714196998817</v>
+        <v>0.00162460971996477</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001472025760450746</v>
+        <v>5.748043296447125e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001370931277092177</v>
+        <v>0.001505064369686671</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01177272727272724</v>
+        <v>0.01186321062478934</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01213277747893129</v>
+        <v>0.01471450258974815</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0007005629523724661</v>
+        <v>0.001345595788392418</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0007970528424708134</v>
+        <v>0.001531554603588536</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000248976602017259</v>
+        <v>0.00158798346838103</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00613762933898677</v>
+        <v>0.01336589795646863</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01648778645177536</v>
+        <v>0.0135254343993956</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001236075413716745</v>
+        <v>0.001051560484333608</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001381656804733733</v>
+        <v>0.001505420699137969</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003568511127797356</v>
+        <v>0.001394149248719881</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009841345391083474</v>
+        <v>0.001013525734163715</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.371325507071423e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002222215188805102</v>
+        <v>0.0009935020054530701</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0001312192454893002</v>
+        <v>0.003047898338220856</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003024618238903939</v>
+        <v>0.001540117550574063</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001982786444324885</v>
+        <v>0.0001063782156219079</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002765183534414309</v>
+        <v>0.002294034810863555</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0002210646496360852</v>
+        <v>0.0004885021153181235</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.003472306575614334</v>
+        <v>0.005848573720100095</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002000714415132443</v>
+        <v>0.001396371671451871</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0001727067858756065</v>
+        <v>0.00169622296246898</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0002113866967305783</v>
+        <v>0.0007882886219206936</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.155124653739407e-05</v>
+        <v>0.0002199973476342376</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0005675745174123226</v>
+        <v>5.369156460236779e-05</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0006362997810137133</v>
+        <v>0.00174454288649204</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.00199691681488281</v>
+        <v>0.002891356565144737</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>0.0003054101221640459</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.155124653738573e-05</v>
+        <v>0.0003071078478206951</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002541041343223474</v>
+        <v>0.00138257439389419</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001968996564512581</v>
+        <v>0.003516059389396914</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.00016042780748661</v>
+        <v>0.0001246537396121822</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002693045328554996</v>
+        <v>0.0008331487517007463</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.002309633530831737</v>
+        <v>0.001710027683529963</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001273860488541917</v>
+        <v>0.001423027367221333</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0006570059401246942</v>
+        <v>-0.0009921979262909331</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0020614239632538</v>
+        <v>0.001305704099821742</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0002860434390663857</v>
+        <v>0.0003841316958216684</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.455467869222243e-05</v>
+        <v>0.00091697777947089</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>0.0001006290188612313</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.498001805406602e-17</v>
+        <v>0.001602718857180943</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.003136429763206103</v>
+        <v>-0.0001268542856279642</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.003249849697813448</v>
+        <v>0.0007761243478828949</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.001703460536999152</v>
+        <v>7.341121838977394e-06</v>
       </c>
       <c r="BC8" t="n">
-        <v>9.405752618422691e-05</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>0.0004299433598075802</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>0.0004187248859481851</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.001787878787878747</v>
+        <v>0.003111041704908607</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.0008427800495544203</v>
+        <v>-0.001382700018224883</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0004265466048973238</v>
+        <v>-3.866136465224829e-06</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-0.0003968488669910147</v>
+        <v>0.000675700172210661</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0008925140793273028</v>
+        <v>0.001328286270926693</v>
       </c>
       <c r="BL8" t="n">
-        <v>7.367387033400396e-05</v>
+        <v>0.0003260399152464788</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.000461184596342018</v>
+        <v>0.0003043485197983337</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001385498255246123</v>
+        <v>-0.0007769823471911158</v>
       </c>
       <c r="BO8" t="n">
-        <v>-0.001235460285809265</v>
+        <v>0.001518423206239358</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0005645161290322941</v>
+        <v>0.0007122845878899497</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>3.683693516699782e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0002016129032258396</v>
+        <v>0.0009750108860750813</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.000552032001611849</v>
+        <v>0.0003653605575908853</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001097990187323355</v>
+        <v>0.000457915475432144</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>0.001237101401493426</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001447247342535291</v>
+        <v>0.001248291416074388</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001184076308740262</v>
+        <v>0.0007415527278652551</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.367387033400396e-05</v>
+        <v>4.010695187165459e-05</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0005666464739536303</v>
+        <v>0.0004286412512218701</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0</v>
+        <v>6.811761684643314e-05</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.641306324330963e-05</v>
+        <v>0.0002584943583735288</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0001464851674935486</v>
+        <v>0.0003281289347771333</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0008110948191593387</v>
+        <v>0.0006054385175264631</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0008695040252209684</v>
+        <v>9.654335328983521e-05</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0002236359833640234</v>
+        <v>9.825400822630337e-05</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0002407208176438969</v>
+        <v>0.0008828223058992057</v>
       </c>
       <c r="CJ8" t="n">
-        <v>8.455467869222799e-05</v>
+        <v>0.0007971119587339703</v>
       </c>
       <c r="CK8" t="n">
-        <v>4.032258064518291e-05</v>
+        <v>-3.683693516699227e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001831501831501881</v>
+        <v>0.00653241650294697</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003657880580957495</v>
+        <v>0.004273084479371347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004181818181818142</v>
+        <v>0.003143418467583492</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00248484848484849</v>
+        <v>0.001203558346415534</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002302459445316618</v>
+        <v>0.005943025540275071</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002897838899803573</v>
+        <v>0.00430790960451981</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00060606060606061</v>
+        <v>0.000363636363636366</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008363636363636306</v>
+        <v>0.02175757575757571</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02024432809773125</v>
+        <v>0.01654545454545452</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02012798138452589</v>
+        <v>0.01972789115646264</v>
       </c>
       <c r="M9" t="n">
+        <v>0.005913978494623618</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002795698924731127</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.004273084479371347</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.01988487702773423</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.02757718472004191</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.01678787878787879</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.004223968565815361</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.007261968800430296</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.00378192534381141</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.00121212121212122</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.007757575757575697</v>
       </c>
-      <c r="N9" t="n">
-        <v>0.005648330058939133</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.004518558364712199</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.02315299592786503</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.03109198493813876</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.01145454545454542</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.002354788069073832</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.008552985476062369</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.004764243614931263</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.0008064516129032695</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.01599999999999999</v>
-      </c>
       <c r="X9" t="n">
-        <v>0.002161100196463672</v>
+        <v>0.006279434850863463</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.006737967914438458</v>
+        <v>0.002205486820871394</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.005294117647058771</v>
+        <v>0.004666666666666586</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004424242424242364</v>
+        <v>0.006969696969696904</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0004911591355599599</v>
+        <v>0.0005817335660267542</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.006166375799883672</v>
+        <v>0.00672727272727266</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.004133961276818443</v>
+        <v>0.002878074306645795</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.007154384077460996</v>
+        <v>0.002302459445316651</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.002617801047120394</v>
+        <v>0.002554027504911593</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0002139037433154911</v>
+        <v>0.0007891770011274057</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0007878787878787929</v>
+        <v>0.0008606777837546487</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.003438113948919452</v>
+        <v>0.002946954813359537</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01460151250727165</v>
+        <v>0.01276818419675566</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.000303030303030305</v>
+        <v>0.0006279434850864129</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0004911591355599487</v>
+        <v>0.001570680628272236</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.01000581733566028</v>
+        <v>0.004424242424242353</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.01134380453752182</v>
+        <v>0.006331763474620666</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0005540166204985875</v>
+        <v>0.001578354002254823</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.009939393939393892</v>
+        <v>0.004552590266876033</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.004013961605584626</v>
+        <v>0.005917159763313562</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.001613770844540052</v>
+        <v>0.002151694459386711</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.005119255381035481</v>
+        <v>0.001866404715127712</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.006545454545454498</v>
+        <v>0.01032813340505644</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0008064516129032695</v>
+        <v>0.001977894124490975</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.000969696969696976</v>
+        <v>0.004479348458406096</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0004911591355599376</v>
+        <v>0.001098901098901139</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0003929273084479656</v>
+        <v>0.004013961605584704</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.006060606060606</v>
+        <v>0.003192046049188979</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.008320251177394055</v>
+        <v>0.01229722658294092</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.006907378335949788</v>
+        <v>0.009837781266352753</v>
       </c>
       <c r="BC9" t="n">
+        <v>0.0004303388918773243</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.00057561486132921</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.007090909090909025</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.004948897256589524</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.001080550098231825</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.0002673796791443639</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.004363001745200745</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.004484848484848447</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.001183765501691103</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.005468295520651601</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.006993006993006945</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.01344809037116726</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.001882732651963348</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.000430338891877291</v>
+      </c>
+      <c r="BR9" t="n">
         <v>0.001575757575757575</v>
       </c>
-      <c r="BD9" t="n">
-        <v>5.540166204985875e-05</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.005454545454545401</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0.009037116729424411</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0.0004278074866309933</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0.001090909090909098</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>5.636978579481866e-05</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.01515151515151514</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.000484848484848488</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.004969696969696913</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0.002259279182356089</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.01212121212121209</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0.003657880580957495</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0.000484848484848488</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0.001522593320235777</v>
-      </c>
       <c r="BS9" t="n">
-        <v>0.003339882121807503</v>
+        <v>0.003438113948919475</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.003757575757575715</v>
+        <v>0.001515151515151514</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.002652259332023621</v>
+        <v>0.002242424242424212</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.002040816326530659</v>
+        <v>0.002848722986247554</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.003880157170923393</v>
+        <v>0.001240135287485922</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0001662049861495762</v>
+        <v>9.823182711199419e-05</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0003878116343490112</v>
+        <v>0.0006355932203390147</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002313071543840772</v>
+        <v>0.0007326007326007745</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001696969696969697</v>
+        <v>0.0003382187147689009</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.003438113948919497</v>
+        <v>0.001080550098231869</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>5.347593582887278e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.00044321329639887</v>
+        <v>0.001977401129943512</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.001129666011787844</v>
+        <v>0.001227897838899816</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002603143418467613</v>
+        <v>0.0006355932203390147</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0007756232686980224</v>
+        <v>0.0008606777837546597</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002258064516129099</v>
+        <v>0.002996070726915523</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.003929273084479401</v>
+        <v>0.002420656266810073</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.001129666011787833</v>
+        <v>0.001221640488656184</v>
       </c>
     </row>
   </sheetData>
